--- a/artfynd/A 45924-2023 artfynd.xlsx
+++ b/artfynd/A 45924-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY132"/>
+  <dimension ref="A1:AY129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135323944</v>
+        <v>135322207</v>
       </c>
       <c r="B2" t="n">
-        <v>97435</v>
+        <v>92220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621245</v>
+        <v>621161</v>
       </c>
       <c r="R2" t="n">
-        <v>7322005</v>
+        <v>7322085</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,41 +766,30 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135322207</v>
+        <v>135322208</v>
       </c>
       <c r="B3" t="n">
-        <v>92220</v>
+        <v>92201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621161</v>
+        <v>621277</v>
       </c>
       <c r="R3" t="n">
-        <v>7322085</v>
+        <v>7322024</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135322208</v>
+        <v>135323158</v>
       </c>
       <c r="B4" t="n">
         <v>92201</v>
@@ -939,14 +928,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621277</v>
+        <v>621508</v>
       </c>
       <c r="R4" t="n">
-        <v>7322024</v>
+        <v>7322064</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +977,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Koll påse</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,12 +997,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1019,7 +1013,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135323158</v>
+        <v>135360046</v>
       </c>
       <c r="B5" t="n">
         <v>92201</v>
@@ -1048,19 +1042,22 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621508</v>
+        <v>621248</v>
       </c>
       <c r="R5" t="n">
-        <v>7322064</v>
+        <v>7322029</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,12 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Koll påse</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,18 +1105,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1908,7 +1901,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135323940</v>
+        <v>135325606</v>
       </c>
       <c r="B13" t="n">
         <v>92245</v>
@@ -1939,17 +1932,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621170</v>
+        <v>621546</v>
       </c>
       <c r="R13" t="n">
-        <v>7322082</v>
+        <v>7322049</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1978,7 +1971,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1988,12 +1981,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:36</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Död fruktkropp</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,38 +1992,27 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Gammal granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135323942</v>
+        <v>135325614</v>
       </c>
       <c r="B14" t="n">
         <v>92245</v>
@@ -2066,14 +2043,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621193</v>
+        <v>621499</v>
       </c>
       <c r="R14" t="n">
-        <v>7322034</v>
+        <v>7322020</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2105,7 +2082,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2115,7 +2092,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2126,38 +2103,27 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Grov granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135325606</v>
+        <v>135325615</v>
       </c>
       <c r="B15" t="n">
         <v>92245</v>
@@ -2192,13 +2158,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621546</v>
+        <v>621477</v>
       </c>
       <c r="R15" t="n">
-        <v>7322049</v>
+        <v>7322015</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2227,7 +2193,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2237,7 +2203,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,7 +2234,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135325614</v>
+        <v>135326363</v>
       </c>
       <c r="B16" t="n">
         <v>92245</v>
@@ -2299,17 +2265,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621499</v>
+        <v>621274</v>
       </c>
       <c r="R16" t="n">
-        <v>7322020</v>
+        <v>7322030</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2338,7 +2304,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2314,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,12 +2329,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2379,7 +2345,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135325615</v>
+        <v>135326494</v>
       </c>
       <c r="B17" t="n">
         <v>92245</v>
@@ -2410,14 +2376,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>621477</v>
+        <v>621284</v>
       </c>
       <c r="R17" t="n">
-        <v>7322015</v>
+        <v>7321988</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2449,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2459,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2474,12 +2440,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2490,7 +2456,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135326363</v>
+        <v>135330944</v>
       </c>
       <c r="B18" t="n">
         <v>92245</v>
@@ -2521,17 +2487,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>621274</v>
+        <v>621163</v>
       </c>
       <c r="R18" t="n">
-        <v>7322030</v>
+        <v>7322149</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2560,7 +2526,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2570,7 +2536,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2585,12 +2551,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2601,7 +2567,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135326494</v>
+        <v>135330962</v>
       </c>
       <c r="B19" t="n">
         <v>92245</v>
@@ -2632,17 +2598,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621284</v>
+        <v>621313</v>
       </c>
       <c r="R19" t="n">
-        <v>7321988</v>
+        <v>7322173</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2671,7 +2637,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2681,7 +2647,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,12 +2662,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2712,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135330944</v>
+        <v>135323152</v>
       </c>
       <c r="B20" t="n">
-        <v>92245</v>
+        <v>79452</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2723,37 +2689,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>621163</v>
+        <v>621500</v>
       </c>
       <c r="R20" t="n">
-        <v>7322149</v>
+        <v>7322090</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2782,7 +2748,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2792,7 +2758,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,12 +2773,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2823,10 +2789,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135330962</v>
+        <v>135323160</v>
       </c>
       <c r="B21" t="n">
-        <v>92245</v>
+        <v>79452</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2834,37 +2800,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>621313</v>
+        <v>621529</v>
       </c>
       <c r="R21" t="n">
-        <v>7322173</v>
+        <v>7322033</v>
       </c>
       <c r="S21" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2893,7 +2859,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2903,7 +2869,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2918,12 +2884,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2934,7 +2900,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135323152</v>
+        <v>135326516</v>
       </c>
       <c r="B22" t="n">
         <v>79452</v>
@@ -2969,13 +2935,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>621500</v>
+        <v>621266</v>
       </c>
       <c r="R22" t="n">
-        <v>7322090</v>
+        <v>7322033</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3004,7 +2970,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3014,7 +2980,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3029,12 +2995,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3045,7 +3011,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135323160</v>
+        <v>135329849</v>
       </c>
       <c r="B23" t="n">
         <v>79452</v>
@@ -3076,17 +3042,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>621529</v>
+        <v>621260</v>
       </c>
       <c r="R23" t="n">
-        <v>7322033</v>
+        <v>7322039</v>
       </c>
       <c r="S23" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3140,12 +3106,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3156,7 +3122,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135326516</v>
+        <v>135329856</v>
       </c>
       <c r="B24" t="n">
         <v>79452</v>
@@ -3187,14 +3153,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>621266</v>
+        <v>621374</v>
       </c>
       <c r="R24" t="n">
-        <v>7322033</v>
+        <v>7322008</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3226,7 +3192,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3236,7 +3202,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,12 +3217,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3267,7 +3233,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135329849</v>
+        <v>135329858</v>
       </c>
       <c r="B25" t="n">
         <v>79452</v>
@@ -3302,10 +3268,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>621260</v>
+        <v>621401</v>
       </c>
       <c r="R25" t="n">
-        <v>7322039</v>
+        <v>7322018</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3337,7 +3303,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3347,7 +3313,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3378,45 +3344,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135329856</v>
+        <v>135359947</v>
       </c>
       <c r="B26" t="n">
-        <v>79452</v>
+        <v>92689</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>898</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>621374</v>
+        <v>621212</v>
       </c>
       <c r="R26" t="n">
-        <v>7322008</v>
+        <v>7321996</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3448,7 +3417,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,7 +3427,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3467,18 +3436,19 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3489,48 +3459,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135329858</v>
+        <v>135323154</v>
       </c>
       <c r="B27" t="n">
-        <v>79452</v>
+        <v>92795</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>864</v>
+        <v>918</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>621401</v>
+        <v>621513</v>
       </c>
       <c r="R27" t="n">
-        <v>7322018</v>
+        <v>7322084</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3559,7 +3529,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3569,7 +3539,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3584,12 +3554,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3600,7 +3570,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135323154</v>
+        <v>135323161</v>
       </c>
       <c r="B28" t="n">
         <v>92795</v>
@@ -3635,10 +3605,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>621513</v>
+        <v>621535</v>
       </c>
       <c r="R28" t="n">
-        <v>7322084</v>
+        <v>7322033</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3670,7 +3640,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3680,7 +3650,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3711,7 +3681,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135323161</v>
+        <v>135325596</v>
       </c>
       <c r="B29" t="n">
         <v>92795</v>
@@ -3742,17 +3712,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>621535</v>
+        <v>621469</v>
       </c>
       <c r="R29" t="n">
-        <v>7322033</v>
+        <v>7322105</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3781,7 +3751,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3791,7 +3761,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3806,12 +3776,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3822,7 +3792,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135325596</v>
+        <v>135325607</v>
       </c>
       <c r="B30" t="n">
         <v>92795</v>
@@ -3857,13 +3827,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>621469</v>
+        <v>621551</v>
       </c>
       <c r="R30" t="n">
-        <v>7322105</v>
+        <v>7322047</v>
       </c>
       <c r="S30" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3892,7 +3862,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3902,7 +3872,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3933,7 +3903,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135325607</v>
+        <v>135325611</v>
       </c>
       <c r="B31" t="n">
         <v>92795</v>
@@ -3968,13 +3938,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>621551</v>
+        <v>621536</v>
       </c>
       <c r="R31" t="n">
-        <v>7322047</v>
+        <v>7322045</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4003,7 +3973,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4013,7 +3983,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4044,7 +4014,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135325611</v>
+        <v>135325619</v>
       </c>
       <c r="B32" t="n">
         <v>92795</v>
@@ -4079,13 +4049,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>621536</v>
+        <v>621430</v>
       </c>
       <c r="R32" t="n">
-        <v>7322045</v>
+        <v>7321973</v>
       </c>
       <c r="S32" t="n">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4114,7 +4084,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4124,7 +4094,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4155,7 +4125,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135325619</v>
+        <v>135325628</v>
       </c>
       <c r="B33" t="n">
         <v>92795</v>
@@ -4190,10 +4160,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>621430</v>
+        <v>621396</v>
       </c>
       <c r="R33" t="n">
-        <v>7321973</v>
+        <v>7322008</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4225,7 +4195,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4235,7 +4205,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4266,7 +4236,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135325628</v>
+        <v>135326490</v>
       </c>
       <c r="B34" t="n">
         <v>92795</v>
@@ -4297,14 +4267,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>621396</v>
+        <v>621245</v>
       </c>
       <c r="R34" t="n">
-        <v>7322008</v>
+        <v>7322039</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4336,7 +4306,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4346,7 +4316,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4361,12 +4331,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4377,7 +4347,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135326490</v>
+        <v>135330955</v>
       </c>
       <c r="B35" t="n">
         <v>92795</v>
@@ -4408,17 +4378,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>621245</v>
+        <v>621277</v>
       </c>
       <c r="R35" t="n">
-        <v>7322039</v>
+        <v>7322229</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4447,7 +4417,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4457,7 +4427,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4472,12 +4442,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4488,48 +4458,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135330955</v>
+        <v>135323157</v>
       </c>
       <c r="B36" t="n">
-        <v>92795</v>
+        <v>91970</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>918</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>621277</v>
+        <v>621507</v>
       </c>
       <c r="R36" t="n">
-        <v>7322229</v>
+        <v>7322061</v>
       </c>
       <c r="S36" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4558,7 +4528,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4568,7 +4538,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4583,12 +4553,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4599,7 +4569,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135323157</v>
+        <v>135323537</v>
       </c>
       <c r="B37" t="n">
         <v>91970</v>
@@ -4630,17 +4600,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>621507</v>
+        <v>621393</v>
       </c>
       <c r="R37" t="n">
-        <v>7322061</v>
+        <v>7322163</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4669,7 +4639,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4679,7 +4649,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4694,23 +4664,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135323537</v>
+        <v>135323538</v>
       </c>
       <c r="B38" t="n">
         <v>91970</v>
@@ -4745,13 +4711,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>621393</v>
+        <v>621368</v>
       </c>
       <c r="R38" t="n">
-        <v>7322163</v>
+        <v>7322188</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4780,7 +4746,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4790,7 +4756,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4817,7 +4783,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135323538</v>
+        <v>135325610</v>
       </c>
       <c r="B39" t="n">
         <v>91970</v>
@@ -4848,17 +4814,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>621368</v>
+        <v>621539</v>
       </c>
       <c r="R39" t="n">
-        <v>7322188</v>
+        <v>7322038</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4887,7 +4853,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4897,7 +4863,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4912,19 +4878,23 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135325610</v>
+        <v>135325613</v>
       </c>
       <c r="B40" t="n">
         <v>91970</v>
@@ -4959,13 +4929,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>621539</v>
+        <v>621495</v>
       </c>
       <c r="R40" t="n">
-        <v>7322038</v>
+        <v>7322020</v>
       </c>
       <c r="S40" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4994,7 +4964,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5004,7 +4974,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5035,7 +5005,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135325613</v>
+        <v>135325621</v>
       </c>
       <c r="B41" t="n">
         <v>91970</v>
@@ -5070,13 +5040,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>621495</v>
+        <v>621385</v>
       </c>
       <c r="R41" t="n">
-        <v>7322020</v>
+        <v>7321984</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5105,7 +5075,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5115,7 +5085,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5146,7 +5116,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135325621</v>
+        <v>135326368</v>
       </c>
       <c r="B42" t="n">
         <v>91970</v>
@@ -5177,17 +5147,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>621385</v>
+        <v>621346</v>
       </c>
       <c r="R42" t="n">
-        <v>7321984</v>
+        <v>7322011</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5216,7 +5186,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5226,7 +5196,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5241,12 +5211,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5257,7 +5227,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135326368</v>
+        <v>135329807</v>
       </c>
       <c r="B43" t="n">
         <v>91970</v>
@@ -5288,17 +5258,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>621346</v>
+        <v>621435</v>
       </c>
       <c r="R43" t="n">
-        <v>7322011</v>
+        <v>7322135</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5327,7 +5297,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5337,7 +5307,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Stående död gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5352,12 +5327,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5368,10 +5343,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135329807</v>
+        <v>135323539</v>
       </c>
       <c r="B44" t="n">
-        <v>91970</v>
+        <v>91974</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5379,37 +5354,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>621435</v>
+        <v>621368</v>
       </c>
       <c r="R44" t="n">
-        <v>7322135</v>
+        <v>7322169</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5438,7 +5413,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5448,12 +5423,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Stående död gran</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5468,23 +5438,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135323539</v>
+        <v>135325608</v>
       </c>
       <c r="B45" t="n">
         <v>91974</v>
@@ -5515,17 +5481,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>621368</v>
+        <v>621550</v>
       </c>
       <c r="R45" t="n">
-        <v>7322169</v>
+        <v>7322047</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5554,7 +5520,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5564,7 +5530,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5579,19 +5545,23 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135325608</v>
+        <v>135325617</v>
       </c>
       <c r="B46" t="n">
         <v>91974</v>
@@ -5626,13 +5596,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>621550</v>
+        <v>621477</v>
       </c>
       <c r="R46" t="n">
-        <v>7322047</v>
+        <v>7322015</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5661,7 +5631,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5671,7 +5641,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5702,7 +5672,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135325617</v>
+        <v>135325631</v>
       </c>
       <c r="B47" t="n">
         <v>91974</v>
@@ -5737,13 +5707,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>621477</v>
+        <v>621324</v>
       </c>
       <c r="R47" t="n">
-        <v>7322015</v>
+        <v>7322178</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5772,7 +5742,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5782,7 +5752,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5813,7 +5783,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135325631</v>
+        <v>135326370</v>
       </c>
       <c r="B48" t="n">
         <v>91974</v>
@@ -5844,17 +5814,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>621324</v>
+        <v>621362</v>
       </c>
       <c r="R48" t="n">
-        <v>7322178</v>
+        <v>7322015</v>
       </c>
       <c r="S48" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5883,7 +5853,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5893,7 +5863,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5908,12 +5878,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5924,7 +5894,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135326370</v>
+        <v>135326374</v>
       </c>
       <c r="B49" t="n">
         <v>91974</v>
@@ -5959,13 +5929,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>621362</v>
+        <v>621407</v>
       </c>
       <c r="R49" t="n">
-        <v>7322015</v>
+        <v>7322006</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5994,7 +5964,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6004,7 +5974,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6035,7 +6005,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135326374</v>
+        <v>135326488</v>
       </c>
       <c r="B50" t="n">
         <v>91974</v>
@@ -6066,17 +6036,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>621407</v>
+        <v>621223</v>
       </c>
       <c r="R50" t="n">
-        <v>7322006</v>
+        <v>7322025</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6105,7 +6075,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6115,7 +6085,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6130,12 +6100,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6146,7 +6116,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135326488</v>
+        <v>135326491</v>
       </c>
       <c r="B51" t="n">
         <v>91974</v>
@@ -6181,13 +6151,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>621223</v>
+        <v>621281</v>
       </c>
       <c r="R51" t="n">
-        <v>7322025</v>
+        <v>7322013</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6216,7 +6186,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6226,7 +6196,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6257,7 +6227,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135326491</v>
+        <v>135326493</v>
       </c>
       <c r="B52" t="n">
         <v>91974</v>
@@ -6292,10 +6262,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>621281</v>
+        <v>621282</v>
       </c>
       <c r="R52" t="n">
-        <v>7322013</v>
+        <v>7321987</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6327,7 +6297,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6337,7 +6307,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6368,7 +6338,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135326493</v>
+        <v>135326528</v>
       </c>
       <c r="B53" t="n">
         <v>91974</v>
@@ -6399,17 +6369,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>621282</v>
+        <v>621179</v>
       </c>
       <c r="R53" t="n">
-        <v>7321987</v>
+        <v>7321981</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6438,7 +6408,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6448,7 +6418,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6463,12 +6433,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6479,7 +6449,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135326528</v>
+        <v>135330949</v>
       </c>
       <c r="B54" t="n">
         <v>91974</v>
@@ -6510,17 +6480,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>621179</v>
+        <v>621255</v>
       </c>
       <c r="R54" t="n">
-        <v>7321981</v>
+        <v>7322247</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6549,7 +6519,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6559,7 +6529,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6574,12 +6544,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6590,7 +6560,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135330949</v>
+        <v>135330959</v>
       </c>
       <c r="B55" t="n">
         <v>91974</v>
@@ -6625,13 +6595,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>621255</v>
+        <v>621325</v>
       </c>
       <c r="R55" t="n">
-        <v>7322247</v>
+        <v>7322254</v>
       </c>
       <c r="S55" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6660,7 +6630,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6670,7 +6640,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6701,48 +6671,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135330959</v>
+        <v>135329809</v>
       </c>
       <c r="B56" t="n">
-        <v>91974</v>
+        <v>91988</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>621325</v>
+        <v>621360</v>
       </c>
       <c r="R56" t="n">
-        <v>7322254</v>
+        <v>7322150</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6771,7 +6741,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6781,7 +6751,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Låga</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6796,12 +6771,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6812,7 +6787,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135329809</v>
+        <v>135330960</v>
       </c>
       <c r="B57" t="n">
         <v>91988</v>
@@ -6843,17 +6818,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>621360</v>
+        <v>621326</v>
       </c>
       <c r="R57" t="n">
-        <v>7322150</v>
+        <v>7322247</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6882,7 +6857,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6892,12 +6867,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Låga</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6912,12 +6882,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6928,7 +6898,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135330960</v>
+        <v>135330963</v>
       </c>
       <c r="B58" t="n">
         <v>91988</v>
@@ -6963,13 +6933,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>621326</v>
+        <v>621313</v>
       </c>
       <c r="R58" t="n">
-        <v>7322247</v>
+        <v>7322173</v>
       </c>
       <c r="S58" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6998,7 +6968,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7008,7 +6978,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7039,48 +7009,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135330963</v>
+        <v>135323148</v>
       </c>
       <c r="B59" t="n">
-        <v>91988</v>
+        <v>83222</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>621313</v>
+        <v>621493</v>
       </c>
       <c r="R59" t="n">
-        <v>7322173</v>
+        <v>7322104</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7109,7 +7079,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7119,7 +7089,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7134,12 +7104,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7150,10 +7120,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135323943</v>
+        <v>135323159</v>
       </c>
       <c r="B60" t="n">
-        <v>92406</v>
+        <v>83222</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7161,34 +7131,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>621195</v>
+        <v>621497</v>
       </c>
       <c r="R60" t="n">
-        <v>7322035</v>
+        <v>7322062</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7220,7 +7190,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7230,7 +7200,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7241,38 +7211,27 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Grov granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135323148</v>
+        <v>135325599</v>
       </c>
       <c r="B61" t="n">
         <v>83222</v>
@@ -7303,17 +7262,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
         <v>621493</v>
       </c>
       <c r="R61" t="n">
-        <v>7322104</v>
+        <v>7322087</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7367,12 +7326,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7383,7 +7342,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135323159</v>
+        <v>135325601</v>
       </c>
       <c r="B62" t="n">
         <v>83222</v>
@@ -7414,14 +7373,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>621497</v>
+        <v>621522</v>
       </c>
       <c r="R62" t="n">
-        <v>7322062</v>
+        <v>7322095</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7453,7 +7412,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7463,7 +7422,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Cinnoberflamlav</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7478,12 +7442,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7494,7 +7458,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135325599</v>
+        <v>135325603</v>
       </c>
       <c r="B63" t="n">
         <v>83222</v>
@@ -7529,13 +7493,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>621493</v>
+        <v>621524</v>
       </c>
       <c r="R63" t="n">
-        <v>7322087</v>
+        <v>7322055</v>
       </c>
       <c r="S63" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7564,7 +7528,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7574,7 +7538,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7605,7 +7569,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135325601</v>
+        <v>135325625</v>
       </c>
       <c r="B64" t="n">
         <v>83222</v>
@@ -7640,10 +7604,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>621522</v>
+        <v>621351</v>
       </c>
       <c r="R64" t="n">
-        <v>7322095</v>
+        <v>7322003</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7675,7 +7639,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7685,12 +7649,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Cinnoberflamlav</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7721,7 +7680,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135325603</v>
+        <v>135326511</v>
       </c>
       <c r="B65" t="n">
         <v>83222</v>
@@ -7752,17 +7711,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>621524</v>
+        <v>621157</v>
       </c>
       <c r="R65" t="n">
-        <v>7322055</v>
+        <v>7322072</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7791,7 +7750,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7801,7 +7760,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7816,12 +7775,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7832,7 +7791,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135325625</v>
+        <v>135326520</v>
       </c>
       <c r="B66" t="n">
         <v>83222</v>
@@ -7863,17 +7822,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>621351</v>
+        <v>621266</v>
       </c>
       <c r="R66" t="n">
-        <v>7322003</v>
+        <v>7322031</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7902,7 +7861,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7912,7 +7871,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7927,12 +7886,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7943,7 +7902,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135326511</v>
+        <v>135329841</v>
       </c>
       <c r="B67" t="n">
         <v>83222</v>
@@ -7974,14 +7933,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>621157</v>
+        <v>621163</v>
       </c>
       <c r="R67" t="n">
-        <v>7322072</v>
+        <v>7322058</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8013,7 +7972,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8023,7 +7982,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8038,12 +7997,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8054,48 +8013,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135326520</v>
+        <v>135326367</v>
       </c>
       <c r="B68" t="n">
-        <v>83222</v>
+        <v>92329</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>1506</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>621266</v>
+        <v>621316</v>
       </c>
       <c r="R68" t="n">
-        <v>7322031</v>
+        <v>7322007</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8124,7 +8083,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8134,7 +8093,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8149,12 +8108,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8165,48 +8124,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135329841</v>
+        <v>135326373</v>
       </c>
       <c r="B69" t="n">
-        <v>83222</v>
+        <v>92329</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>1506</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>621163</v>
+        <v>621407</v>
       </c>
       <c r="R69" t="n">
-        <v>7322058</v>
+        <v>7322006</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8235,7 +8194,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8245,7 +8204,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8260,12 +8219,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8276,7 +8235,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135326367</v>
+        <v>135326376</v>
       </c>
       <c r="B70" t="n">
         <v>92329</v>
@@ -8311,13 +8270,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>621316</v>
+        <v>621413</v>
       </c>
       <c r="R70" t="n">
-        <v>7322007</v>
+        <v>7322044</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8346,7 +8305,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8356,7 +8315,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8387,48 +8346,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135326373</v>
+        <v>135323164</v>
       </c>
       <c r="B71" t="n">
-        <v>92329</v>
+        <v>92167</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1506</v>
+        <v>1588</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>621407</v>
+        <v>621465</v>
       </c>
       <c r="R71" t="n">
-        <v>7322006</v>
+        <v>7322032</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8457,7 +8416,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8467,7 +8426,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8482,12 +8441,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8498,10 +8457,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135326376</v>
+        <v>135323540</v>
       </c>
       <c r="B72" t="n">
-        <v>92329</v>
+        <v>92318</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8509,37 +8468,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1506</v>
+        <v>2062</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>621413</v>
+        <v>621368</v>
       </c>
       <c r="R72" t="n">
-        <v>7322044</v>
+        <v>7322169</v>
       </c>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8568,7 +8527,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8578,7 +8537,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8593,64 +8552,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135323164</v>
+        <v>135330951</v>
       </c>
       <c r="B73" t="n">
-        <v>92167</v>
+        <v>92318</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1588</v>
+        <v>2062</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>621465</v>
+        <v>621257</v>
       </c>
       <c r="R73" t="n">
-        <v>7322032</v>
+        <v>7322248</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8679,7 +8634,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8689,7 +8644,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8704,12 +8659,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8720,48 +8675,52 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135323540</v>
+        <v>135323941</v>
       </c>
       <c r="B74" t="n">
-        <v>92318</v>
+        <v>96678</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2062</v>
+        <v>2166</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>621368</v>
+        <v>621202</v>
       </c>
       <c r="R74" t="n">
-        <v>7322169</v>
+        <v>7322052</v>
       </c>
       <c r="S74" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8790,7 +8749,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8800,7 +8759,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8809,66 +8768,86 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Grov kraftig nedbruten tallåga # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135330951</v>
+        <v>135323167</v>
       </c>
       <c r="B75" t="n">
-        <v>92318</v>
+        <v>91937</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>621257</v>
+        <v>621418</v>
       </c>
       <c r="R75" t="n">
-        <v>7322248</v>
+        <v>7321963</v>
       </c>
       <c r="S75" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8897,7 +8876,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8907,7 +8886,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8922,12 +8901,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8938,10 +8917,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135323941</v>
+        <v>135323542</v>
       </c>
       <c r="B76" t="n">
-        <v>96678</v>
+        <v>91937</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8949,37 +8928,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2166</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>621202</v>
+        <v>621359</v>
       </c>
       <c r="R76" t="n">
-        <v>7322052</v>
+        <v>7322116</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9008,7 +8987,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9018,74 +8997,59 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Grov kraftig nedbruten tallåga # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135323167</v>
+        <v>135323149</v>
       </c>
       <c r="B77" t="n">
-        <v>91937</v>
+        <v>79373</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9095,13 +9059,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>621418</v>
+        <v>621499</v>
       </c>
       <c r="R77" t="n">
-        <v>7321963</v>
+        <v>7322092</v>
       </c>
       <c r="S77" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9130,7 +9094,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9140,7 +9104,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9171,48 +9135,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135323542</v>
+        <v>135323155</v>
       </c>
       <c r="B78" t="n">
-        <v>91937</v>
+        <v>79373</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>621359</v>
+        <v>621518</v>
       </c>
       <c r="R78" t="n">
-        <v>7322116</v>
+        <v>7322064</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9241,7 +9205,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9251,7 +9215,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9266,19 +9230,23 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135323149</v>
+        <v>135323173</v>
       </c>
       <c r="B79" t="n">
         <v>79373</v>
@@ -9313,13 +9281,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>621499</v>
+        <v>621355</v>
       </c>
       <c r="R79" t="n">
-        <v>7322092</v>
+        <v>7321983</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9348,7 +9316,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9358,7 +9326,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9389,7 +9357,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135323155</v>
+        <v>135325598</v>
       </c>
       <c r="B80" t="n">
         <v>79373</v>
@@ -9420,17 +9388,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>621518</v>
+        <v>621493</v>
       </c>
       <c r="R80" t="n">
-        <v>7322064</v>
+        <v>7322096</v>
       </c>
       <c r="S80" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9459,7 +9427,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9469,7 +9437,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9484,12 +9452,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9500,7 +9468,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135323173</v>
+        <v>135325620</v>
       </c>
       <c r="B81" t="n">
         <v>79373</v>
@@ -9531,17 +9499,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>621355</v>
+        <v>621429</v>
       </c>
       <c r="R81" t="n">
-        <v>7321983</v>
+        <v>7321989</v>
       </c>
       <c r="S81" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9570,7 +9538,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9580,7 +9548,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9595,12 +9563,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9611,7 +9579,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135325598</v>
+        <v>135325622</v>
       </c>
       <c r="B82" t="n">
         <v>79373</v>
@@ -9646,13 +9614,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>621493</v>
+        <v>621392</v>
       </c>
       <c r="R82" t="n">
-        <v>7322096</v>
+        <v>7321985</v>
       </c>
       <c r="S82" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9681,7 +9649,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9691,7 +9659,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9722,7 +9690,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135325620</v>
+        <v>135326492</v>
       </c>
       <c r="B83" t="n">
         <v>79373</v>
@@ -9753,17 +9721,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>621429</v>
+        <v>621275</v>
       </c>
       <c r="R83" t="n">
-        <v>7321989</v>
+        <v>7322022</v>
       </c>
       <c r="S83" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9792,7 +9760,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9802,7 +9770,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9817,12 +9785,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9833,7 +9801,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135325622</v>
+        <v>135326518</v>
       </c>
       <c r="B84" t="n">
         <v>79373</v>
@@ -9864,17 +9832,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>621392</v>
+        <v>621266</v>
       </c>
       <c r="R84" t="n">
-        <v>7321985</v>
+        <v>7322033</v>
       </c>
       <c r="S84" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9903,7 +9871,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9913,7 +9881,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9928,12 +9896,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9944,7 +9912,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135326492</v>
+        <v>135329852</v>
       </c>
       <c r="B85" t="n">
         <v>79373</v>
@@ -9975,17 +9943,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>621275</v>
+        <v>621266</v>
       </c>
       <c r="R85" t="n">
-        <v>7322022</v>
+        <v>7322030</v>
       </c>
       <c r="S85" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10014,7 +9982,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10024,7 +9992,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10039,12 +10007,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -10055,7 +10023,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135326518</v>
+        <v>135329854</v>
       </c>
       <c r="B86" t="n">
         <v>79373</v>
@@ -10086,14 +10054,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>621266</v>
+        <v>621314</v>
       </c>
       <c r="R86" t="n">
-        <v>7322033</v>
+        <v>7322003</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10125,7 +10093,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10135,7 +10103,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10150,12 +10118,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10166,48 +10134,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135329852</v>
+        <v>135326484</v>
       </c>
       <c r="B87" t="n">
-        <v>79373</v>
+        <v>78776</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>621266</v>
+        <v>621167</v>
       </c>
       <c r="R87" t="n">
-        <v>7322030</v>
+        <v>7322046</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10236,7 +10204,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10246,7 +10214,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10261,12 +10229,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10277,48 +10245,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135329854</v>
+        <v>135323162</v>
       </c>
       <c r="B88" t="n">
-        <v>79373</v>
+        <v>83341</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>621314</v>
+        <v>621495</v>
       </c>
       <c r="R88" t="n">
-        <v>7322003</v>
+        <v>7322022</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10347,7 +10315,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10357,7 +10325,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10372,12 +10340,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10388,10 +10356,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135326484</v>
+        <v>135323147</v>
       </c>
       <c r="B89" t="n">
-        <v>78776</v>
+        <v>83358</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10399,37 +10367,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>621167</v>
+        <v>621480</v>
       </c>
       <c r="R89" t="n">
-        <v>7322046</v>
+        <v>7322096</v>
       </c>
       <c r="S89" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10458,7 +10426,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10468,7 +10436,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10483,12 +10451,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10499,32 +10467,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135323162</v>
+        <v>135323151</v>
       </c>
       <c r="B90" t="n">
-        <v>83341</v>
+        <v>83358</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10534,13 +10502,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>621495</v>
+        <v>621502</v>
       </c>
       <c r="R90" t="n">
-        <v>7322022</v>
+        <v>7322088</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10569,7 +10537,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10579,7 +10547,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10610,7 +10578,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135323147</v>
+        <v>135325600</v>
       </c>
       <c r="B91" t="n">
         <v>83358</v>
@@ -10641,17 +10609,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>621480</v>
+        <v>621487</v>
       </c>
       <c r="R91" t="n">
-        <v>7322096</v>
+        <v>7322053</v>
       </c>
       <c r="S91" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10680,7 +10648,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10690,7 +10658,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10705,12 +10673,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10721,7 +10689,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135323151</v>
+        <v>135325602</v>
       </c>
       <c r="B92" t="n">
         <v>83358</v>
@@ -10752,17 +10720,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>621502</v>
+        <v>621515</v>
       </c>
       <c r="R92" t="n">
-        <v>7322088</v>
+        <v>7322081</v>
       </c>
       <c r="S92" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10791,7 +10759,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10801,7 +10769,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10816,12 +10784,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10832,7 +10800,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135325600</v>
+        <v>135325609</v>
       </c>
       <c r="B93" t="n">
         <v>83358</v>
@@ -10867,13 +10835,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>621487</v>
+        <v>621545</v>
       </c>
       <c r="R93" t="n">
-        <v>7322053</v>
+        <v>7322048</v>
       </c>
       <c r="S93" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10902,7 +10870,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10912,7 +10880,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10943,7 +10911,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135325602</v>
+        <v>135325618</v>
       </c>
       <c r="B94" t="n">
         <v>83358</v>
@@ -10978,13 +10946,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>621515</v>
+        <v>621472</v>
       </c>
       <c r="R94" t="n">
-        <v>7322081</v>
+        <v>7322001</v>
       </c>
       <c r="S94" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11013,7 +10981,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11023,7 +10991,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11054,7 +11022,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135325609</v>
+        <v>135325624</v>
       </c>
       <c r="B95" t="n">
         <v>83358</v>
@@ -11089,13 +11057,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>621545</v>
+        <v>621351</v>
       </c>
       <c r="R95" t="n">
-        <v>7322048</v>
+        <v>7322003</v>
       </c>
       <c r="S95" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11124,7 +11092,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11134,7 +11102,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11165,7 +11133,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135325618</v>
+        <v>135326486</v>
       </c>
       <c r="B96" t="n">
         <v>83358</v>
@@ -11196,17 +11164,17 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>621472</v>
+        <v>621203</v>
       </c>
       <c r="R96" t="n">
-        <v>7322001</v>
+        <v>7322017</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11235,7 +11203,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11245,7 +11213,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11260,12 +11228,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11276,7 +11244,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135325624</v>
+        <v>135326495</v>
       </c>
       <c r="B97" t="n">
         <v>83358</v>
@@ -11307,14 +11275,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>621351</v>
+        <v>621271</v>
       </c>
       <c r="R97" t="n">
-        <v>7322003</v>
+        <v>7321971</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11346,7 +11314,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11356,7 +11324,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11371,12 +11339,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11387,7 +11355,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135326486</v>
+        <v>135326523</v>
       </c>
       <c r="B98" t="n">
         <v>83358</v>
@@ -11418,14 +11386,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>621203</v>
+        <v>621284</v>
       </c>
       <c r="R98" t="n">
-        <v>7322017</v>
+        <v>7322012</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11457,7 +11425,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11467,7 +11435,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11482,12 +11450,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11498,7 +11466,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135326495</v>
+        <v>135329844</v>
       </c>
       <c r="B99" t="n">
         <v>83358</v>
@@ -11529,17 +11497,17 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>621271</v>
+        <v>621207</v>
       </c>
       <c r="R99" t="n">
-        <v>7321971</v>
+        <v>7322034</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11568,7 +11536,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11578,7 +11546,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11593,12 +11561,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11609,32 +11577,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135326523</v>
+        <v>135323153</v>
       </c>
       <c r="B100" t="n">
-        <v>83358</v>
+        <v>78731</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6440</v>
+        <v>6443</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11644,13 +11612,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>621284</v>
+        <v>621513</v>
       </c>
       <c r="R100" t="n">
-        <v>7322012</v>
+        <v>7322084</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11679,7 +11647,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11689,7 +11657,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>På torr grangren</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11704,12 +11677,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11720,10 +11693,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135329844</v>
+        <v>135322206</v>
       </c>
       <c r="B101" t="n">
-        <v>83358</v>
+        <v>79992</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11731,37 +11704,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>621207</v>
+        <v>621158</v>
       </c>
       <c r="R101" t="n">
-        <v>7322034</v>
+        <v>7322094</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11790,7 +11763,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11800,7 +11773,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11815,12 +11788,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11831,32 +11804,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135323153</v>
+        <v>135323169</v>
       </c>
       <c r="B102" t="n">
-        <v>78731</v>
+        <v>79992</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6443</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11866,13 +11839,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>621513</v>
+        <v>621411</v>
       </c>
       <c r="R102" t="n">
-        <v>7322084</v>
+        <v>7321964</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11901,7 +11874,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11911,12 +11884,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>På torr grangren</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11947,7 +11915,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135322206</v>
+        <v>135325627</v>
       </c>
       <c r="B103" t="n">
         <v>79992</v>
@@ -11978,17 +11946,17 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>621158</v>
+        <v>621323</v>
       </c>
       <c r="R103" t="n">
-        <v>7322094</v>
+        <v>7321957</v>
       </c>
       <c r="S103" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12017,7 +11985,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12027,7 +11995,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12042,12 +12010,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12058,7 +12026,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135323169</v>
+        <v>135325629</v>
       </c>
       <c r="B104" t="n">
         <v>79992</v>
@@ -12089,17 +12057,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>621411</v>
+        <v>621316</v>
       </c>
       <c r="R104" t="n">
-        <v>7321964</v>
+        <v>7322179</v>
       </c>
       <c r="S104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12128,7 +12096,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12138,7 +12106,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12153,12 +12121,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12169,7 +12137,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135325627</v>
+        <v>135329808</v>
       </c>
       <c r="B105" t="n">
         <v>79992</v>
@@ -12200,17 +12168,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>621323</v>
+        <v>621315</v>
       </c>
       <c r="R105" t="n">
-        <v>7321957</v>
+        <v>7322181</v>
       </c>
       <c r="S105" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12239,7 +12207,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12249,7 +12217,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12264,12 +12237,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -12280,7 +12253,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135325629</v>
+        <v>135330953</v>
       </c>
       <c r="B106" t="n">
         <v>79992</v>
@@ -12311,17 +12284,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>621316</v>
+        <v>621277</v>
       </c>
       <c r="R106" t="n">
-        <v>7322179</v>
+        <v>7322238</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12350,7 +12323,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12360,7 +12333,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12375,12 +12348,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -12391,10 +12364,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135329808</v>
+        <v>135325633</v>
       </c>
       <c r="B107" t="n">
-        <v>79992</v>
+        <v>78377</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12402,37 +12375,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>621315</v>
+        <v>621287</v>
       </c>
       <c r="R107" t="n">
-        <v>7322181</v>
+        <v>7322205</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12461,7 +12434,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12471,12 +12444,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12491,12 +12459,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -12507,10 +12475,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135330953</v>
+        <v>135330943</v>
       </c>
       <c r="B108" t="n">
-        <v>79992</v>
+        <v>78377</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12518,21 +12486,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12542,13 +12510,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>621277</v>
+        <v>621177</v>
       </c>
       <c r="R108" t="n">
-        <v>7322238</v>
+        <v>7322135</v>
       </c>
       <c r="S108" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12577,7 +12545,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12587,7 +12555,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12618,7 +12586,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135325633</v>
+        <v>135330946</v>
       </c>
       <c r="B109" t="n">
         <v>78377</v>
@@ -12649,17 +12617,17 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>621287</v>
+        <v>621194</v>
       </c>
       <c r="R109" t="n">
-        <v>7322205</v>
+        <v>7322206</v>
       </c>
       <c r="S109" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12688,7 +12656,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12698,7 +12666,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12713,12 +12681,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -12729,10 +12697,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135330943</v>
+        <v>135323175</v>
       </c>
       <c r="B110" t="n">
-        <v>78377</v>
+        <v>57975</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12740,37 +12708,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>621177</v>
+        <v>621152</v>
       </c>
       <c r="R110" t="n">
-        <v>7322135</v>
+        <v>7321996</v>
       </c>
       <c r="S110" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12799,7 +12772,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12809,7 +12782,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12824,12 +12797,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -12840,10 +12813,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135330946</v>
+        <v>135323536</v>
       </c>
       <c r="B111" t="n">
-        <v>78377</v>
+        <v>57975</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12851,34 +12824,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>621194</v>
+        <v>621461</v>
       </c>
       <c r="R111" t="n">
-        <v>7322206</v>
+        <v>7322142</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12910,7 +12883,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12920,7 +12893,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12935,23 +12913,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135323175</v>
+        <v>135326366</v>
       </c>
       <c r="B112" t="n">
         <v>57975</v>
@@ -12980,24 +12954,27 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>621152</v>
+        <v>621323</v>
       </c>
       <c r="R112" t="n">
-        <v>7321996</v>
+        <v>7322015</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13026,7 +13003,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13036,7 +13013,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13051,12 +13033,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -13067,7 +13049,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135323536</v>
+        <v>135326496</v>
       </c>
       <c r="B113" t="n">
         <v>57975</v>
@@ -13096,19 +13078,27 @@
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>621461</v>
+        <v>621246</v>
       </c>
       <c r="R113" t="n">
-        <v>7322142</v>
+        <v>7321956</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13137,7 +13127,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13147,12 +13137,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13167,19 +13157,23 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135326366</v>
+        <v>135326497</v>
       </c>
       <c r="B114" t="n">
         <v>57975</v>
@@ -13218,17 +13212,17 @@
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>621323</v>
+        <v>621165</v>
       </c>
       <c r="R114" t="n">
-        <v>7322015</v>
+        <v>7322002</v>
       </c>
       <c r="S114" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13257,7 +13251,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13267,12 +13261,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13287,12 +13281,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -13303,7 +13297,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135326496</v>
+        <v>135329838</v>
       </c>
       <c r="B115" t="n">
         <v>57975</v>
@@ -13332,27 +13326,19 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>621246</v>
+        <v>621123</v>
       </c>
       <c r="R115" t="n">
-        <v>7321956</v>
+        <v>7322113</v>
       </c>
       <c r="S115" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13381,7 +13367,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13391,12 +13377,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13411,12 +13397,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -13427,7 +13413,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135326497</v>
+        <v>135329861</v>
       </c>
       <c r="B116" t="n">
         <v>57975</v>
@@ -13456,27 +13442,19 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
+          <t>Maskaure Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>621165</v>
+        <v>621226</v>
       </c>
       <c r="R116" t="n">
-        <v>7322002</v>
+        <v>7322073</v>
       </c>
       <c r="S116" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13505,7 +13483,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13515,12 +13493,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack.</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13535,12 +13513,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -13551,7 +13529,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135329838</v>
+        <v>135330957</v>
       </c>
       <c r="B117" t="n">
         <v>57975</v>
@@ -13580,19 +13558,24 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>621123</v>
+        <v>621320</v>
       </c>
       <c r="R117" t="n">
-        <v>7322113</v>
+        <v>7322249</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13621,7 +13604,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13631,12 +13614,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13651,12 +13634,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -13667,7 +13650,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135329861</v>
+        <v>135330964</v>
       </c>
       <c r="B118" t="n">
         <v>57975</v>
@@ -13696,19 +13679,27 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>621226</v>
+        <v>621397</v>
       </c>
       <c r="R118" t="n">
-        <v>7322073</v>
+        <v>7322108</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13737,7 +13728,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13747,12 +13738,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13767,12 +13758,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -13783,7 +13774,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135330957</v>
+        <v>135330965</v>
       </c>
       <c r="B119" t="n">
         <v>57975</v>
@@ -13812,24 +13803,27 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>621320</v>
+        <v>621436</v>
       </c>
       <c r="R119" t="n">
-        <v>7322249</v>
+        <v>7322109</v>
       </c>
       <c r="S119" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13858,7 +13852,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13868,12 +13862,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13904,7 +13898,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135330964</v>
+        <v>135330966</v>
       </c>
       <c r="B120" t="n">
         <v>57975</v>
@@ -13937,7 +13931,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -13947,13 +13941,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>621397</v>
+        <v>621459</v>
       </c>
       <c r="R120" t="n">
-        <v>7322108</v>
+        <v>7322135</v>
       </c>
       <c r="S120" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13982,7 +13976,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13992,12 +13986,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14028,7 +14022,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135330965</v>
+        <v>135330967</v>
       </c>
       <c r="B121" t="n">
         <v>57975</v>
@@ -14071,13 +14065,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>621436</v>
+        <v>621219</v>
       </c>
       <c r="R121" t="n">
-        <v>7322109</v>
+        <v>7322131</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14106,7 +14100,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14116,12 +14110,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Spår av födosök</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14152,40 +14146,44 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135330966</v>
+        <v>135330945</v>
       </c>
       <c r="B122" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -14195,13 +14193,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>621459</v>
+        <v>621163</v>
       </c>
       <c r="R122" t="n">
-        <v>7322135</v>
+        <v>7322161</v>
       </c>
       <c r="S122" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14230,7 +14228,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14240,12 +14238,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Uppflygande</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14276,10 +14274,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135330967</v>
+        <v>135326371</v>
       </c>
       <c r="B123" t="n">
-        <v>57975</v>
+        <v>58136</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14287,45 +14285,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>621219</v>
+        <v>621395</v>
       </c>
       <c r="R123" t="n">
-        <v>7322131</v>
+        <v>7322009</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14354,7 +14344,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14364,12 +14354,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Spår av födosök</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14384,12 +14369,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -14400,32 +14385,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135330945</v>
+        <v>135326513</v>
       </c>
       <c r="B124" t="n">
-        <v>57162</v>
+        <v>41606</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100138</v>
+        <v>215713</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -14433,27 +14418,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>621163</v>
+        <v>621171</v>
       </c>
       <c r="R124" t="n">
-        <v>7322161</v>
+        <v>7322040</v>
       </c>
       <c r="S124" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14482,7 +14459,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14492,12 +14469,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14512,12 +14484,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -14528,48 +14500,48 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135326371</v>
+        <v>135326512</v>
       </c>
       <c r="B125" t="n">
-        <v>58136</v>
+        <v>98066</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>621395</v>
+        <v>621161</v>
       </c>
       <c r="R125" t="n">
-        <v>7322009</v>
+        <v>7322070</v>
       </c>
       <c r="S125" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14598,7 +14570,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14608,7 +14580,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14623,12 +14595,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -14639,59 +14611,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>135323938</v>
+        <v>135326487</v>
       </c>
       <c r="B126" t="n">
-        <v>6286</v>
+        <v>78382</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>105336</v>
+        <v>228579</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>621155</v>
+        <v>621204</v>
       </c>
       <c r="R126" t="n">
-        <v>7322085</v>
+        <v>7322016</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14723,7 +14681,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14733,12 +14691,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>På fläckporing</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14753,22 +14706,26 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>135326513</v>
+        <v>135326521</v>
       </c>
       <c r="B127" t="n">
-        <v>41606</v>
+        <v>78382</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14776,38 +14733,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>215713</v>
+        <v>228579</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>621171</v>
+        <v>621266</v>
       </c>
       <c r="R127" t="n">
-        <v>7322040</v>
+        <v>7322030</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14839,7 +14792,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14849,7 +14802,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14880,32 +14833,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>135326512</v>
+        <v>135326526</v>
       </c>
       <c r="B128" t="n">
-        <v>98066</v>
+        <v>78382</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221941</v>
+        <v>228579</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14915,10 +14868,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>621161</v>
+        <v>621284</v>
       </c>
       <c r="R128" t="n">
-        <v>7322070</v>
+        <v>7322006</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14950,7 +14903,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14960,7 +14913,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14991,10 +14944,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>135326487</v>
+        <v>135326483</v>
       </c>
       <c r="B129" t="n">
-        <v>78382</v>
+        <v>79396</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15002,21 +14955,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228579</v>
+        <v>260591</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15026,13 +14979,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>621204</v>
+        <v>621165</v>
       </c>
       <c r="R129" t="n">
-        <v>7322016</v>
+        <v>7322074</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15061,7 +15014,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15071,7 +15024,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15095,339 +15048,6 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>135326521</v>
-      </c>
-      <c r="B130" t="n">
-        <v>78382</v>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E130" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>Skornjamyran, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q130" t="n">
-        <v>621266</v>
-      </c>
-      <c r="R130" t="n">
-        <v>7322030</v>
-      </c>
-      <c r="S130" t="n">
-        <v>10</v>
-      </c>
-      <c r="T130" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AD130" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE130" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG130" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT130" t="inlineStr"/>
-      <c r="AW130" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>135326526</v>
-      </c>
-      <c r="B131" t="n">
-        <v>78382</v>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E131" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>Skornjamyran, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q131" t="n">
-        <v>621284</v>
-      </c>
-      <c r="R131" t="n">
-        <v>7322006</v>
-      </c>
-      <c r="S131" t="n">
-        <v>10</v>
-      </c>
-      <c r="T131" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AD131" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE131" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG131" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT131" t="inlineStr"/>
-      <c r="AW131" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>135326483</v>
-      </c>
-      <c r="B132" t="n">
-        <v>79396</v>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E132" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="P132" t="inlineStr">
-        <is>
-          <t>Maskaure Skornjamyran / Renskötartjärnen, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q132" t="n">
-        <v>621165</v>
-      </c>
-      <c r="R132" t="n">
-        <v>7322074</v>
-      </c>
-      <c r="S132" t="n">
-        <v>8</v>
-      </c>
-      <c r="T132" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W132" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AD132" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE132" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG132" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT132" t="inlineStr"/>
-      <c r="AW132" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/A 45924-2023 artfynd.xlsx
+++ b/artfynd/A 45924-2023 artfynd.xlsx
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">

--- a/artfynd/A 45924-2023 artfynd.xlsx
+++ b/artfynd/A 45924-2023 artfynd.xlsx
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">

--- a/artfynd/A 45924-2023 artfynd.xlsx
+++ b/artfynd/A 45924-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -15013,7 +15013,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">

--- a/artfynd/A 45924-2023 artfynd.xlsx
+++ b/artfynd/A 45924-2023 artfynd.xlsx
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Martin Axegård, Christina Boyd, Laura de Jong</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">

--- a/artfynd/A 45924-2023 artfynd.xlsx
+++ b/artfynd/A 45924-2023 artfynd.xlsx
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Martin Axegård, Christina Boyd, Laura de Jong</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">

--- a/artfynd/A 45924-2023 artfynd.xlsx
+++ b/artfynd/A 45924-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY134"/>
+  <dimension ref="A1:AZ134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323944</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322207</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322208</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323158</t>
         </is>
       </c>
     </row>
@@ -1251,6 +1276,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135360046</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1362,6 +1392,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323166</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1473,6 +1508,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323172</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1584,6 +1624,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330954</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1695,6 +1740,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322209</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1806,6 +1856,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323170</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1917,6 +1972,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323174</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2024,6 +2084,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323544</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2155,6 +2220,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323940</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2281,6 +2351,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323942</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2392,6 +2467,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325606</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2503,6 +2583,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325614</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2614,6 +2699,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325615</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2725,6 +2815,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326363</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2836,6 +2931,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326494</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2947,6 +3047,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330944</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3058,6 +3163,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330962</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3169,6 +3279,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323152</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3280,6 +3395,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323160</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3391,6 +3511,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326516</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3502,6 +3627,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329849</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3613,6 +3743,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329856</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3722,6 +3857,11 @@
       <c r="AY28" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329858</t>
         </is>
       </c>
     </row>
@@ -3839,6 +3979,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135359947</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3950,6 +4095,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323154</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4061,6 +4211,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323161</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4172,6 +4327,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325596</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4283,6 +4443,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325607</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4394,6 +4559,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325611</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4505,6 +4675,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325619</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4616,6 +4791,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325628</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4727,6 +4907,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326490</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4838,6 +5023,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330955</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4949,6 +5139,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323157</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5056,6 +5251,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323537</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5163,6 +5363,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323538</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5274,6 +5479,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325610</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5385,6 +5595,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325613</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5496,6 +5711,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325621</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5607,6 +5827,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326368</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5723,6 +5948,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329807</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5830,6 +6060,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323539</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5941,6 +6176,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325608</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6052,6 +6292,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325617</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6163,6 +6408,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325631</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6274,6 +6524,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326370</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6385,6 +6640,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326374</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6496,6 +6756,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326488</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6607,6 +6872,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326491</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6718,6 +6988,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326493</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6829,6 +7104,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326528</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6940,6 +7220,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330949</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7051,6 +7336,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330959</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7167,6 +7457,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329809</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7278,6 +7573,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330960</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7389,6 +7689,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330963</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7515,6 +7820,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323943</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7626,6 +7936,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323148</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7737,6 +8052,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323159</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7848,6 +8168,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325599</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7964,6 +8289,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325601</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8075,6 +8405,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325603</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8186,6 +8521,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325625</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8297,6 +8637,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326511</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8408,6 +8753,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326520</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8519,6 +8869,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329841</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8630,6 +8985,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326367</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8741,6 +9101,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326373</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8852,6 +9217,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326376</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8963,6 +9333,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323164</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9070,6 +9445,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323540</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9179,6 +9559,11 @@
       <c r="AY77" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330951</t>
         </is>
       </c>
     </row>
@@ -9312,6 +9697,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323941</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9423,6 +9813,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323167</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9530,6 +9925,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323542</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9641,6 +10041,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323149</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9752,6 +10157,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323155</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9863,6 +10273,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323173</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9974,6 +10389,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325598</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10085,6 +10505,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325620</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10196,6 +10621,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325622</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10307,6 +10737,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326492</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10418,6 +10853,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326518</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10529,6 +10969,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329852</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10640,6 +11085,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329854</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10751,6 +11201,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326484</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10862,6 +11317,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323162</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10973,6 +11433,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323147</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11084,6 +11549,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323151</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11195,6 +11665,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325600</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11306,6 +11781,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325602</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11417,6 +11897,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325609</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11528,6 +12013,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325618</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11639,6 +12129,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325624</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11750,6 +12245,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326486</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11861,6 +12361,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326495</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11972,6 +12477,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326523</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12083,6 +12593,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329844</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12199,6 +12714,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323153</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12310,6 +12830,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322206</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12421,6 +12946,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323169</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12532,6 +13062,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325627</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12643,6 +13178,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325629</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12759,6 +13299,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329808</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12870,6 +13415,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330953</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12981,6 +13531,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325633</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13092,6 +13647,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330943</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13203,6 +13763,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330946</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13319,6 +13884,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323175</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13431,6 +14001,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323536</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13555,6 +14130,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326366</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13679,6 +14259,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326496</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13803,6 +14388,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326497</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13919,6 +14509,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329838</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14035,6 +14630,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329861</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14156,6 +14756,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330957</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14280,6 +14885,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330964</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14404,6 +15014,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330965</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14528,6 +15143,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330966</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14652,6 +15272,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330967</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14780,6 +15405,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330945</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14891,6 +15521,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326371</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15021,6 +15656,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323938</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15136,6 +15776,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326513</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15247,6 +15892,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326512</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15358,6 +16008,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326487</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15469,6 +16124,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326521</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15580,6 +16240,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326526</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15691,8 +16356,148 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326483</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 45924-2023 artfynd.xlsx
+++ b/artfynd/A 45924-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135323944</v>
       </c>
       <c r="B2" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>135322207</v>
       </c>
       <c r="B3" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135322208</v>
       </c>
       <c r="B4" t="n">
-        <v>92201</v>
+        <v>92243</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>135323158</v>
       </c>
       <c r="B5" t="n">
-        <v>92201</v>
+        <v>92243</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>135360046</v>
       </c>
       <c r="B6" t="n">
-        <v>92201</v>
+        <v>92243</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>135323166</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>135323172</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>135330954</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>135322209</v>
       </c>
       <c r="B10" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>135323170</v>
       </c>
       <c r="B11" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>135323174</v>
       </c>
       <c r="B12" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>135323544</v>
       </c>
       <c r="B13" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>135323940</v>
       </c>
       <c r="B14" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135323942</v>
       </c>
       <c r="B15" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>135325606</v>
       </c>
       <c r="B16" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135325614</v>
       </c>
       <c r="B17" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>135325615</v>
       </c>
       <c r="B18" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>135326363</v>
       </c>
       <c r="B19" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>135326494</v>
       </c>
       <c r="B20" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135330944</v>
       </c>
       <c r="B21" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135330962</v>
       </c>
       <c r="B22" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>135323152</v>
       </c>
       <c r="B23" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>135323160</v>
       </c>
       <c r="B24" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>135326516</v>
       </c>
       <c r="B25" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>135329849</v>
       </c>
       <c r="B26" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>135329856</v>
       </c>
       <c r="B27" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>135329858</v>
       </c>
       <c r="B28" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>135359947</v>
       </c>
       <c r="B29" t="n">
-        <v>92689</v>
+        <v>92731</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>135323154</v>
       </c>
       <c r="B30" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>135323161</v>
       </c>
       <c r="B31" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>135325596</v>
       </c>
       <c r="B32" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>135325607</v>
       </c>
       <c r="B33" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>135325611</v>
       </c>
       <c r="B34" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>135325619</v>
       </c>
       <c r="B35" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>135325628</v>
       </c>
       <c r="B36" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>135326490</v>
       </c>
       <c r="B37" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>135330955</v>
       </c>
       <c r="B38" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>135323157</v>
       </c>
       <c r="B39" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>135323537</v>
       </c>
       <c r="B40" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>135323538</v>
       </c>
       <c r="B41" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>135325610</v>
       </c>
       <c r="B42" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>135325613</v>
       </c>
       <c r="B43" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>135325621</v>
       </c>
       <c r="B44" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>135326368</v>
       </c>
       <c r="B45" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135329807</v>
       </c>
       <c r="B46" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>135323539</v>
       </c>
       <c r="B47" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>135325608</v>
       </c>
       <c r="B48" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>135325617</v>
       </c>
       <c r="B49" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>135325631</v>
       </c>
       <c r="B50" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>135326370</v>
       </c>
       <c r="B51" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>135326374</v>
       </c>
       <c r="B52" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>135326488</v>
       </c>
       <c r="B53" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>135326491</v>
       </c>
       <c r="B54" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>135326493</v>
       </c>
       <c r="B55" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>135326528</v>
       </c>
       <c r="B56" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>135330949</v>
       </c>
       <c r="B57" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>135330959</v>
       </c>
       <c r="B58" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         <v>135329809</v>
       </c>
       <c r="B59" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>135330960</v>
       </c>
       <c r="B60" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>135330963</v>
       </c>
       <c r="B61" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>135323943</v>
       </c>
       <c r="B62" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>135323148</v>
       </c>
       <c r="B63" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>135323159</v>
       </c>
       <c r="B64" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>135325599</v>
       </c>
       <c r="B65" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>135325601</v>
       </c>
       <c r="B66" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>135325603</v>
       </c>
       <c r="B67" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>135325625</v>
       </c>
       <c r="B68" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>135326511</v>
       </c>
       <c r="B69" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>135326520</v>
       </c>
       <c r="B70" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>135329841</v>
       </c>
       <c r="B71" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>135326367</v>
       </c>
       <c r="B72" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>135326373</v>
       </c>
       <c r="B73" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>135326376</v>
       </c>
       <c r="B74" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>135323164</v>
       </c>
       <c r="B75" t="n">
-        <v>92167</v>
+        <v>92209</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>135323540</v>
       </c>
       <c r="B76" t="n">
-        <v>92318</v>
+        <v>92360</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>135330951</v>
       </c>
       <c r="B77" t="n">
-        <v>92318</v>
+        <v>92360</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>135323941</v>
       </c>
       <c r="B78" t="n">
-        <v>96678</v>
+        <v>96722</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>135323167</v>
       </c>
       <c r="B79" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>135323542</v>
       </c>
       <c r="B80" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>135323149</v>
       </c>
       <c r="B81" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>135323155</v>
       </c>
       <c r="B82" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>135323173</v>
       </c>
       <c r="B83" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>135325598</v>
       </c>
       <c r="B84" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>135325620</v>
       </c>
       <c r="B85" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>135325622</v>
       </c>
       <c r="B86" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>135326492</v>
       </c>
       <c r="B87" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>135326518</v>
       </c>
       <c r="B88" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>135329852</v>
       </c>
       <c r="B89" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>135329854</v>
       </c>
       <c r="B90" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>135326484</v>
       </c>
       <c r="B91" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>135323162</v>
       </c>
       <c r="B92" t="n">
-        <v>83341</v>
+        <v>83381</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>135323147</v>
       </c>
       <c r="B93" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>135323151</v>
       </c>
       <c r="B94" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>135325600</v>
       </c>
       <c r="B95" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>135325602</v>
       </c>
       <c r="B96" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>135325609</v>
       </c>
       <c r="B97" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>135325618</v>
       </c>
       <c r="B98" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>135325624</v>
       </c>
       <c r="B99" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>135326486</v>
       </c>
       <c r="B100" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>135326495</v>
       </c>
       <c r="B101" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>135326523</v>
       </c>
       <c r="B102" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>135329844</v>
       </c>
       <c r="B103" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>135323153</v>
       </c>
       <c r="B104" t="n">
-        <v>78731</v>
+        <v>78769</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>135322206</v>
       </c>
       <c r="B105" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>135323169</v>
       </c>
       <c r="B106" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>135325627</v>
       </c>
       <c r="B107" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>135325629</v>
       </c>
       <c r="B108" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>135329808</v>
       </c>
       <c r="B109" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>135330953</v>
       </c>
       <c r="B110" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>135325633</v>
       </c>
       <c r="B111" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>135330943</v>
       </c>
       <c r="B112" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>135330946</v>
       </c>
       <c r="B113" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>135323175</v>
       </c>
       <c r="B114" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>135323536</v>
       </c>
       <c r="B115" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>135326366</v>
       </c>
       <c r="B116" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>135326496</v>
       </c>
       <c r="B117" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>135326497</v>
       </c>
       <c r="B118" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>135329838</v>
       </c>
       <c r="B119" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>135329861</v>
       </c>
       <c r="B120" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>135330957</v>
       </c>
       <c r="B121" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>135330964</v>
       </c>
       <c r="B122" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>135330965</v>
       </c>
       <c r="B123" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>135330966</v>
       </c>
       <c r="B124" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>135330967</v>
       </c>
       <c r="B125" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>135330945</v>
       </c>
       <c r="B126" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>135326371</v>
       </c>
       <c r="B127" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>135326513</v>
       </c>
       <c r="B129" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>135326512</v>
       </c>
       <c r="B130" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>135326487</v>
       </c>
       <c r="B131" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>135326521</v>
       </c>
       <c r="B132" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>135326526</v>
       </c>
       <c r="B133" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>135326483</v>
       </c>
       <c r="B134" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 45924-2023 artfynd.xlsx
+++ b/artfynd/A 45924-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135323944</v>
       </c>
       <c r="B2" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>135322207</v>
       </c>
       <c r="B3" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135322208</v>
       </c>
       <c r="B4" t="n">
-        <v>92243</v>
+        <v>92270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>135323158</v>
       </c>
       <c r="B5" t="n">
-        <v>92243</v>
+        <v>92270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>135360046</v>
       </c>
       <c r="B6" t="n">
-        <v>92243</v>
+        <v>92270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>135323166</v>
       </c>
       <c r="B7" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>135323172</v>
       </c>
       <c r="B8" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>135330954</v>
       </c>
       <c r="B9" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>135322209</v>
       </c>
       <c r="B10" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>135323170</v>
       </c>
       <c r="B11" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>135323174</v>
       </c>
       <c r="B12" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>135323544</v>
       </c>
       <c r="B13" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>135323940</v>
       </c>
       <c r="B14" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135323942</v>
       </c>
       <c r="B15" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>135325606</v>
       </c>
       <c r="B16" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135325614</v>
       </c>
       <c r="B17" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>135325615</v>
       </c>
       <c r="B18" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>135326363</v>
       </c>
       <c r="B19" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>135326494</v>
       </c>
       <c r="B20" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135330944</v>
       </c>
       <c r="B21" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135330962</v>
       </c>
       <c r="B22" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>135323152</v>
       </c>
       <c r="B23" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>135323160</v>
       </c>
       <c r="B24" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>135326516</v>
       </c>
       <c r="B25" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>135329849</v>
       </c>
       <c r="B26" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>135329856</v>
       </c>
       <c r="B27" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>135329858</v>
       </c>
       <c r="B28" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>135359947</v>
       </c>
       <c r="B29" t="n">
-        <v>92731</v>
+        <v>92758</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>135323154</v>
       </c>
       <c r="B30" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>135323161</v>
       </c>
       <c r="B31" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>135325596</v>
       </c>
       <c r="B32" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>135325607</v>
       </c>
       <c r="B33" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>135325611</v>
       </c>
       <c r="B34" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>135325619</v>
       </c>
       <c r="B35" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>135325628</v>
       </c>
       <c r="B36" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>135326490</v>
       </c>
       <c r="B37" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>135330955</v>
       </c>
       <c r="B38" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>135323157</v>
       </c>
       <c r="B39" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>135323537</v>
       </c>
       <c r="B40" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>135323538</v>
       </c>
       <c r="B41" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>135325610</v>
       </c>
       <c r="B42" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>135325613</v>
       </c>
       <c r="B43" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>135325621</v>
       </c>
       <c r="B44" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>135326368</v>
       </c>
       <c r="B45" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135329807</v>
       </c>
       <c r="B46" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>135323539</v>
       </c>
       <c r="B47" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>135325608</v>
       </c>
       <c r="B48" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>135325617</v>
       </c>
       <c r="B49" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>135325631</v>
       </c>
       <c r="B50" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>135326370</v>
       </c>
       <c r="B51" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>135326374</v>
       </c>
       <c r="B52" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>135326488</v>
       </c>
       <c r="B53" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>135326491</v>
       </c>
       <c r="B54" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>135326493</v>
       </c>
       <c r="B55" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>135326528</v>
       </c>
       <c r="B56" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>135330949</v>
       </c>
       <c r="B57" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>135330959</v>
       </c>
       <c r="B58" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         <v>135329809</v>
       </c>
       <c r="B59" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>135330960</v>
       </c>
       <c r="B60" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>135330963</v>
       </c>
       <c r="B61" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>135323943</v>
       </c>
       <c r="B62" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>135323148</v>
       </c>
       <c r="B63" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>135323159</v>
       </c>
       <c r="B64" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>135325599</v>
       </c>
       <c r="B65" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>135325601</v>
       </c>
       <c r="B66" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>135325603</v>
       </c>
       <c r="B67" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>135325625</v>
       </c>
       <c r="B68" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>135326511</v>
       </c>
       <c r="B69" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>135326520</v>
       </c>
       <c r="B70" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>135329841</v>
       </c>
       <c r="B71" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>135326367</v>
       </c>
       <c r="B72" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>135326373</v>
       </c>
       <c r="B73" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>135326376</v>
       </c>
       <c r="B74" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>135323164</v>
       </c>
       <c r="B75" t="n">
-        <v>92209</v>
+        <v>92236</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>135323540</v>
       </c>
       <c r="B76" t="n">
-        <v>92360</v>
+        <v>92387</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>135330951</v>
       </c>
       <c r="B77" t="n">
-        <v>92360</v>
+        <v>92387</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>135323941</v>
       </c>
       <c r="B78" t="n">
-        <v>96722</v>
+        <v>96749</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>135323167</v>
       </c>
       <c r="B79" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>135323542</v>
       </c>
       <c r="B80" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>135323149</v>
       </c>
       <c r="B81" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>135323155</v>
       </c>
       <c r="B82" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>135323173</v>
       </c>
       <c r="B83" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>135325598</v>
       </c>
       <c r="B84" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>135325620</v>
       </c>
       <c r="B85" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>135325622</v>
       </c>
       <c r="B86" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>135326492</v>
       </c>
       <c r="B87" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>135326518</v>
       </c>
       <c r="B88" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>135329852</v>
       </c>
       <c r="B89" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>135329854</v>
       </c>
       <c r="B90" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>135326484</v>
       </c>
       <c r="B91" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>135323162</v>
       </c>
       <c r="B92" t="n">
-        <v>83381</v>
+        <v>83408</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>135323147</v>
       </c>
       <c r="B93" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>135323151</v>
       </c>
       <c r="B94" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>135325600</v>
       </c>
       <c r="B95" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>135325602</v>
       </c>
       <c r="B96" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>135325609</v>
       </c>
       <c r="B97" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>135325618</v>
       </c>
       <c r="B98" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>135325624</v>
       </c>
       <c r="B99" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>135326486</v>
       </c>
       <c r="B100" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>135326495</v>
       </c>
       <c r="B101" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>135326523</v>
       </c>
       <c r="B102" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>135329844</v>
       </c>
       <c r="B103" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>135323153</v>
       </c>
       <c r="B104" t="n">
-        <v>78769</v>
+        <v>78796</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>135322206</v>
       </c>
       <c r="B105" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>135323169</v>
       </c>
       <c r="B106" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>135325627</v>
       </c>
       <c r="B107" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>135325629</v>
       </c>
       <c r="B108" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>135329808</v>
       </c>
       <c r="B109" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>135330953</v>
       </c>
       <c r="B110" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>135325633</v>
       </c>
       <c r="B111" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>135330943</v>
       </c>
       <c r="B112" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>135330946</v>
       </c>
       <c r="B113" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>135326512</v>
       </c>
       <c r="B130" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>135326487</v>
       </c>
       <c r="B131" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         <v>135326521</v>
       </c>
       <c r="B132" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>135326526</v>
       </c>
       <c r="B133" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>135326483</v>
       </c>
       <c r="B134" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 45924-2023 artfynd.xlsx
+++ b/artfynd/A 45924-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">

--- a/artfynd/A 45924-2023 artfynd.xlsx
+++ b/artfynd/A 45924-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135323944</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>135322207</v>
       </c>
       <c r="B3" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135322208</v>
       </c>
       <c r="B4" t="n">
-        <v>92275</v>
+        <v>92277</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>135323158</v>
       </c>
       <c r="B5" t="n">
-        <v>92275</v>
+        <v>92277</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>135360046</v>
       </c>
       <c r="B6" t="n">
-        <v>92275</v>
+        <v>92277</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>135322209</v>
       </c>
       <c r="B10" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>135323170</v>
       </c>
       <c r="B11" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>135323174</v>
       </c>
       <c r="B12" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>135323544</v>
       </c>
       <c r="B13" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>135323940</v>
       </c>
       <c r="B14" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135323942</v>
       </c>
       <c r="B15" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>135325606</v>
       </c>
       <c r="B16" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>135325614</v>
       </c>
       <c r="B17" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>135325615</v>
       </c>
       <c r="B18" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>135326363</v>
       </c>
       <c r="B19" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>135326494</v>
       </c>
       <c r="B20" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135330944</v>
       </c>
       <c r="B21" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135330962</v>
       </c>
       <c r="B22" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>135359947</v>
       </c>
       <c r="B29" t="n">
-        <v>92763</v>
+        <v>92765</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>135323154</v>
       </c>
       <c r="B30" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>135323161</v>
       </c>
       <c r="B31" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>135325596</v>
       </c>
       <c r="B32" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>135325607</v>
       </c>
       <c r="B33" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>135325611</v>
       </c>
       <c r="B34" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>135325619</v>
       </c>
       <c r="B35" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>135325628</v>
       </c>
       <c r="B36" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>135326490</v>
       </c>
       <c r="B37" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>135330955</v>
       </c>
       <c r="B38" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>135323157</v>
       </c>
       <c r="B39" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>135323537</v>
       </c>
       <c r="B40" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>135323538</v>
       </c>
       <c r="B41" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>135325610</v>
       </c>
       <c r="B42" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>135325613</v>
       </c>
       <c r="B43" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>135325621</v>
       </c>
       <c r="B44" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>135326368</v>
       </c>
       <c r="B45" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135329807</v>
       </c>
       <c r="B46" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>135323539</v>
       </c>
       <c r="B47" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>135325608</v>
       </c>
       <c r="B48" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>135325617</v>
       </c>
       <c r="B49" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>135325631</v>
       </c>
       <c r="B50" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>135326370</v>
       </c>
       <c r="B51" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>135326374</v>
       </c>
       <c r="B52" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>135326488</v>
       </c>
       <c r="B53" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>135326491</v>
       </c>
       <c r="B54" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>135326493</v>
       </c>
       <c r="B55" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>135326528</v>
       </c>
       <c r="B56" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>135330949</v>
       </c>
       <c r="B57" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>135330959</v>
       </c>
       <c r="B58" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         <v>135329809</v>
       </c>
       <c r="B59" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>135330960</v>
       </c>
       <c r="B60" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>135330963</v>
       </c>
       <c r="B61" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>135323943</v>
       </c>
       <c r="B62" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>135326367</v>
       </c>
       <c r="B72" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>135326373</v>
       </c>
       <c r="B73" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>135326376</v>
       </c>
       <c r="B74" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>135323164</v>
       </c>
       <c r="B75" t="n">
-        <v>92241</v>
+        <v>92243</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>135323540</v>
       </c>
       <c r="B76" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>135330951</v>
       </c>
       <c r="B77" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>135323941</v>
       </c>
       <c r="B78" t="n">
-        <v>96754</v>
+        <v>96756</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>135323167</v>
       </c>
       <c r="B79" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>135323542</v>
       </c>
       <c r="B80" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>135326512</v>
       </c>
       <c r="B130" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 45924-2023 artfynd.xlsx
+++ b/artfynd/A 45924-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">

--- a/artfynd/A 45924-2023 artfynd.xlsx
+++ b/artfynd/A 45924-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">

--- a/artfynd/A 45924-2023 artfynd.xlsx
+++ b/artfynd/A 45924-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135323944</v>
       </c>
       <c r="B2" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>135323940</v>
       </c>
       <c r="B14" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135323942</v>
       </c>
       <c r="B15" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>135323943</v>
       </c>
       <c r="B62" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>135323941</v>
       </c>
       <c r="B78" t="n">
-        <v>96756</v>
+        <v>96773</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>135323938</v>
       </c>
       <c r="B128" t="n">
-        <v>6286</v>
+        <v>6288</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
